--- a/static/data/exports/Retro_KA_AE-BP_2020.xlsx
+++ b/static/data/exports/Retro_KA_AE-BP_2020.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,9 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
       <c r="R2" t="n">
         <v>40</v>
       </c>
@@ -635,6 +638,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
         <v>40</v>
       </c>
@@ -694,6 +700,9 @@
           <t>JD(S)</t>
         </is>
       </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
       <c r="R4" t="n">
         <v>40</v>
       </c>
@@ -753,6 +762,9 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
       <c r="R5" t="n">
         <v>40</v>
       </c>
@@ -776,11 +788,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KRaS</t>
+          <t>KRS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19517</v>
+        <v>19524</v>
       </c>
       <c r="E6" t="n">
         <v>628</v>
@@ -811,6 +823,9 @@
         <is>
           <t>KRaS</t>
         </is>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>40</v>
@@ -871,6 +886,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
       <c r="R7" t="n">
         <v>40</v>
       </c>
@@ -930,6 +948,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
       <c r="R8" t="n">
         <v>40</v>
       </c>
@@ -989,6 +1010,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
       <c r="R9" t="n">
         <v>40</v>
       </c>
@@ -1048,6 +1072,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
       <c r="R10" t="n">
         <v>40</v>
       </c>
@@ -1107,6 +1134,9 @@
           <t>RTBHP</t>
         </is>
       </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
       <c r="R11" t="n">
         <v>40</v>
       </c>
@@ -1166,6 +1196,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
       <c r="R12" t="n">
         <v>40</v>
       </c>
@@ -1225,6 +1258,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
       <c r="R13" t="n">
         <v>40</v>
       </c>
@@ -1284,6 +1320,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
       <c r="R14" t="n">
         <v>40</v>
       </c>
@@ -1343,6 +1382,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
       <c r="R15" t="n">
         <v>40</v>
       </c>
@@ -1402,6 +1444,9 @@
           <t>rpsn</t>
         </is>
       </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
       <c r="R16" t="n">
         <v>40</v>
       </c>
@@ -1461,6 +1506,9 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
       <c r="R17" t="n">
         <v>40</v>
       </c>
@@ -1520,6 +1568,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
       <c r="R18" t="n">
         <v>40</v>
       </c>
@@ -1579,6 +1630,9 @@
           <t>JD(S)</t>
         </is>
       </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
       <c r="R19" t="n">
         <v>40</v>
       </c>
@@ -1638,6 +1692,9 @@
           <t>JVBP</t>
         </is>
       </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
       <c r="R20" t="n">
         <v>40</v>
       </c>
@@ -1697,6 +1754,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
       <c r="R21" t="n">
         <v>40</v>
       </c>
@@ -1756,6 +1816,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
       <c r="R22" t="n">
         <v>40</v>
       </c>
@@ -1779,11 +1842,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KRaS</t>
+          <t>KRS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19517</v>
+        <v>19524</v>
       </c>
       <c r="E23" t="n">
         <v>313</v>
@@ -1814,6 +1877,9 @@
         <is>
           <t>KRaS</t>
         </is>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>40</v>
@@ -1874,6 +1940,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
       <c r="R24" t="n">
         <v>40</v>
       </c>
@@ -1933,6 +2002,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
       <c r="R25" t="n">
         <v>40</v>
       </c>
@@ -1992,6 +2064,9 @@
           <t>KAP</t>
         </is>
       </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
       <c r="R26" t="n">
         <v>40</v>
       </c>
@@ -2051,6 +2126,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
       <c r="R27" t="n">
         <v>40</v>
       </c>
@@ -2110,6 +2188,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
       <c r="R28" t="n">
         <v>40</v>
       </c>
@@ -2169,6 +2250,9 @@
           <t>AIJP</t>
         </is>
       </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
       <c r="R29" t="n">
         <v>40</v>
       </c>
@@ -2228,6 +2312,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
       <c r="R30" t="n">
         <v>40</v>
       </c>
@@ -2287,6 +2374,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
       <c r="R31" t="n">
         <v>40</v>
       </c>
@@ -2345,6 +2435,9 @@
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>40</v>
